--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8008,0.0521,0.0582,0.0914</t>
-  </si>
-  <si>
-    <t>0.1024,0.0011,0.0015,0.9693</t>
-  </si>
-  <si>
-    <t>0.6905,0.0072,0.0085,0.4162</t>
-  </si>
-  <si>
-    <t>0.0806,0.0019,0.0015,0.9744</t>
-  </si>
-  <si>
-    <t>0.9966,0.0018,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9946,0.0033,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9945,0.0056,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0032,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0014,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9968,0.0007,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9960,0.0015,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.6172,0.0323,0.4641,0.0118</t>
-  </si>
-  <si>
-    <t>0.2729,0.2948,0.3913,0.0060</t>
-  </si>
-  <si>
-    <t>0.4065,0.0580,0.6265,0.0017</t>
-  </si>
-  <si>
-    <t>0.1932,0.0289,0.7967,0.0058</t>
-  </si>
-  <si>
-    <t>0.8162,0.0314,0.1743,0.0092</t>
-  </si>
-  <si>
-    <t>0.0137,0.9792,0.0133,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.9967,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.1238,0.9065,0.0128,0.0027</t>
-  </si>
-  <si>
-    <t>0.0381,0.9659,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.0332,0.9653,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.7201,0.0394,0.2050,0.0599</t>
-  </si>
-  <si>
-    <t>0.5959,0.0508,0.3028,0.0846</t>
-  </si>
-  <si>
-    <t>0.3022,0.0070,0.8601,0.0018</t>
-  </si>
-  <si>
-    <t>0.1540,0.0367,0.7953,0.0032</t>
-  </si>
-  <si>
-    <t>0.1077,0.0429,0.8492,0.0052</t>
-  </si>
-  <si>
-    <t>0.2303,0.0200,0.7955,0.0107</t>
-  </si>
-  <si>
-    <t>0.0069,0.0016,0.9838,0.0247</t>
-  </si>
-  <si>
-    <t>0.5635,0.4890,0.0284,0.0016</t>
-  </si>
-  <si>
-    <t>0.3532,0.5792,0.1218,0.0096</t>
-  </si>
-  <si>
-    <t>0.0020,0.0118,0.9936,0.0026</t>
-  </si>
-  <si>
-    <t>0.0175,0.9520,0.0523,0.0014</t>
-  </si>
-  <si>
-    <t>0.6910,0.3137,0.0675,0.0458</t>
-  </si>
-  <si>
-    <t>0.8144,0.0612,0.1619,0.0191</t>
-  </si>
-  <si>
-    <t>0.7307,0.3811,0.0116,0.0015</t>
-  </si>
-  <si>
-    <t>0.0510,0.9484,0.0122,0.0039</t>
-  </si>
-  <si>
-    <t>0.0420,0.6306,0.5842,0.0014</t>
-  </si>
-  <si>
-    <t>0.0476,0.1654,0.9340,0.0085</t>
-  </si>
-  <si>
-    <t>0.1203,0.1479,0.8255,0.0091</t>
-  </si>
-  <si>
-    <t>0.1337,0.0252,0.7514,0.0990</t>
-  </si>
-  <si>
-    <t>0.0295,0.0595,0.9370,0.0006</t>
-  </si>
-  <si>
-    <t>0.0068,0.9754,0.0475,0.0004</t>
-  </si>
-  <si>
-    <t>0.0113,0.1193,0.9371,0.0056</t>
-  </si>
-  <si>
-    <t>0.0041,0.9048,0.0047,0.8043</t>
-  </si>
-  <si>
-    <t>0.0449,0.9051,0.0939,0.0248</t>
-  </si>
-  <si>
-    <t>0.0010,0.9948,0.0091,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.9972,0.0132,0.0019</t>
-  </si>
-  <si>
-    <t>0.0136,0.1430,0.9548,0.0009</t>
-  </si>
-  <si>
-    <t>0.0123,0.3330,0.9568,0.0008</t>
-  </si>
-  <si>
-    <t>0.2174,0.0094,0.8273,0.0092</t>
-  </si>
-  <si>
-    <t>0.2156,0.0545,0.7517,0.0141</t>
-  </si>
-  <si>
-    <t>0.0112,0.0053,0.9833,0.0035</t>
-  </si>
-  <si>
-    <t>0.0137,0.0452,0.9670,0.0016</t>
-  </si>
-  <si>
-    <t>0.9280,0.1315,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9585,0.0702,0.0051,0.0010</t>
-  </si>
-  <si>
-    <t>0.9897,0.0039,0.0002,0.0019</t>
-  </si>
-  <si>
-    <t>0.0055,0.1983,0.9787,0.0033</t>
-  </si>
-  <si>
-    <t>0.9852,0.0158,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.9963,0.0033,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9786,0.0219,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.9177,0.9740,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.1379,0.9634,0.0024</t>
-  </si>
-  <si>
-    <t>0.1582,0.0273,0.8778,0.0018</t>
-  </si>
-  <si>
-    <t>0.0024,0.9431,0.7740,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.0041,0.9963,0.0013</t>
-  </si>
-  <si>
-    <t>0.0804,0.8744,0.0425,0.0010</t>
-  </si>
-  <si>
-    <t>0.0169,0.9786,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.7425,0.0308,0.4397,0.0053</t>
-  </si>
-  <si>
-    <t>0.6472,0.2539,0.2051,0.0401</t>
-  </si>
-  <si>
-    <t>0.0199,0.0436,0.9662,0.0008</t>
-  </si>
-  <si>
-    <t>0.0060,0.9677,0.2071,0.0011</t>
-  </si>
-  <si>
-    <t>0.0011,0.9479,0.8394,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9792,0.0385,0.0011</t>
-  </si>
-  <si>
-    <t>0.0028,0.9544,0.5477,0.0002</t>
-  </si>
-  <si>
-    <t>0.2070,0.0008,0.0099,0.8344</t>
-  </si>
-  <si>
-    <t>0.0061,0.0436,0.0011,0.9916</t>
-  </si>
-  <si>
-    <t>0.0117,0.0009,0.0023,0.9877</t>
-  </si>
-  <si>
-    <t>0.0182,0.0405,0.0024,0.9848</t>
-  </si>
-  <si>
-    <t>0.0869,0.0037,0.0044,0.9652</t>
-  </si>
-  <si>
-    <t>0.0053,0.0049,0.0010,0.9956</t>
-  </si>
-  <si>
-    <t>0.0008,0.9545,0.8975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.7747,0.9796,0.0002</t>
-  </si>
-  <si>
-    <t>0.0095,0.5039,0.8910,0.0020</t>
-  </si>
-  <si>
-    <t>0.0330,0.2536,0.8937,0.0022</t>
-  </si>
-  <si>
-    <t>0.0003,0.9951,0.3828,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9782,0.3694,0.0001</t>
-  </si>
-  <si>
-    <t>0.9876,0.0119,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.9810,0.0241,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0088,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0026,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9886,0.0078,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9939,0.0042,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9895,0.0041,0.0003,0.0021</t>
-  </si>
-  <si>
-    <t>0.9927,0.0037,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9981,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9936,0.0041,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9931,0.0033,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9939,0.0015,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9945,0.0023,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9976,0.0004,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0292,0.0050,0.9623,0.0124</t>
-  </si>
-  <si>
-    <t>0.0777,0.0100,0.9478,0.0005</t>
-  </si>
-  <si>
-    <t>0.8850,0.0027,0.0537,0.0237</t>
-  </si>
-  <si>
-    <t>0.3016,0.0067,0.8309,0.0027</t>
-  </si>
-  <si>
-    <t>0.0557,0.9558,0.0054,0.0003</t>
-  </si>
-  <si>
-    <t>0.0112,0.9849,0.0071,0.0004</t>
-  </si>
-  <si>
-    <t>0.1637,0.8889,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.4890,0.6567,0.0047,0.0017</t>
-  </si>
-  <si>
-    <t>0.2204,0.8643,0.0058,0.0011</t>
-  </si>
-  <si>
-    <t>0.0049,0.9927,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.6800,0.4924,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.6107,0.1091,0.3221,0.0138</t>
-  </si>
-  <si>
-    <t>0.1939,0.1806,0.7281,0.0096</t>
-  </si>
-  <si>
-    <t>0.6589,0.0309,0.3521,0.0299</t>
-  </si>
-  <si>
-    <t>0.3793,0.0640,0.6145,0.0059</t>
-  </si>
-  <si>
-    <t>0.2074,0.1016,0.0454,0.8367</t>
-  </si>
-  <si>
-    <t>0.0011,0.9957,0.0087,0.0003</t>
-  </si>
-  <si>
-    <t>0.0044,0.9839,0.0245,0.0149</t>
-  </si>
-  <si>
-    <t>0.0060,0.9782,0.0023,0.0638</t>
-  </si>
-  <si>
-    <t>0.0018,0.9928,0.0655,0.0001</t>
-  </si>
-  <si>
-    <t>0.0538,0.9249,0.0971,0.0013</t>
-  </si>
-  <si>
-    <t>0.5227,0.5748,0.0198,0.0006</t>
-  </si>
-  <si>
-    <t>0.8160,0.2731,0.0061,0.0005</t>
-  </si>
-  <si>
-    <t>0.9838,0.0090,0.0051,0.0010</t>
-  </si>
-  <si>
-    <t>0.9845,0.0149,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9929,0.0021,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9713,0.0276,0.0046,0.0019</t>
-  </si>
-  <si>
-    <t>0.9940,0.0027,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9315,0.0642,0.0138,0.0070</t>
-  </si>
-  <si>
-    <t>0.9858,0.0050,0.0005,0.0038</t>
-  </si>
-  <si>
-    <t>0.9888,0.0061,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.0010,0.9520,0.9144,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.7577,0.9461,0.0001</t>
-  </si>
-  <si>
-    <t>0.0302,0.1385,0.9100,0.0009</t>
-  </si>
-  <si>
-    <t>0.0216,0.0979,0.9400,0.0008</t>
-  </si>
-  <si>
-    <t>0.3372,0.1047,0.5627,0.0253</t>
-  </si>
-  <si>
-    <t>0.6687,0.1326,0.1586,0.0174</t>
-  </si>
-  <si>
-    <t>0.4995,0.0018,0.6474,0.0119</t>
-  </si>
-  <si>
-    <t>0.4804,0.2236,0.2725,0.1760</t>
-  </si>
-  <si>
-    <t>0.2483,0.0007,0.0020,0.9062</t>
-  </si>
-  <si>
-    <t>0.0303,0.0040,0.0005,0.9880</t>
-  </si>
-  <si>
-    <t>0.0043,0.0081,0.0002,0.9968</t>
-  </si>
-  <si>
-    <t>0.0456,0.0029,0.0012,0.9837</t>
-  </si>
-  <si>
-    <t>0.0044,0.9058,0.6663,0.0035</t>
-  </si>
-  <si>
-    <t>0.9815,0.0128,0.0040,0.0012</t>
-  </si>
-  <si>
-    <t>0.1423,0.8409,0.0045,0.0276</t>
-  </si>
-  <si>
-    <t>0.9910,0.0018,0.0007,0.0022</t>
-  </si>
-  <si>
-    <t>0.8805,0.1261,0.0075,0.0066</t>
-  </si>
-  <si>
-    <t>0.9785,0.0081,0.0055,0.0024</t>
-  </si>
-  <si>
-    <t>0.5875,0.0621,0.0156,0.4113</t>
-  </si>
-  <si>
-    <t>0.9653,0.0380,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.1166,0.4406,0.6719,0.0225</t>
-  </si>
-  <si>
-    <t>0.5716,0.0016,0.0065,0.5704</t>
-  </si>
-  <si>
-    <t>0.9373,0.0040,0.0174,0.0241</t>
-  </si>
-  <si>
-    <t>0.7613,0.2325,0.0131,0.0265</t>
-  </si>
-  <si>
-    <t>0.8284,0.1526,0.0325,0.0027</t>
-  </si>
-  <si>
-    <t>0.8468,0.1644,0.0162,0.0021</t>
-  </si>
-  <si>
-    <t>0.6902,0.2407,0.0816,0.0133</t>
-  </si>
-  <si>
-    <t>0.7008,0.2669,0.0485,0.0028</t>
-  </si>
-  <si>
-    <t>0.7681,0.2540,0.0170,0.0038</t>
-  </si>
-  <si>
-    <t>0.9936,0.0036,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9937,0.0101,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9898,0.0012,0.0002,0.0052</t>
-  </si>
-  <si>
-    <t>0.9820,0.0110,0.0076,0.0006</t>
-  </si>
-  <si>
-    <t>0.9731,0.0200,0.0058,0.0034</t>
-  </si>
-  <si>
-    <t>0.9890,0.0050,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9964,0.0007,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9934,0.0030,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.7688,0.3704,0.0063,0.0012</t>
-  </si>
-  <si>
-    <t>0.2731,0.8046,0.0070,0.0005</t>
-  </si>
-  <si>
-    <t>0.6611,0.4507,0.0105,0.0010</t>
-  </si>
-  <si>
-    <t>0.7125,0.1623,0.1852,0.0080</t>
-  </si>
-  <si>
-    <t>0.9248,0.1033,0.0056,0.0014</t>
-  </si>
-  <si>
-    <t>0.8880,0.0886,0.0508,0.0042</t>
-  </si>
-  <si>
-    <t>0.9726,0.0346,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.8582,0.1436,0.0200,0.0052</t>
-  </si>
-  <si>
-    <t>0.0113,0.0335,0.9895,0.0003</t>
-  </si>
-  <si>
-    <t>0.9712,0.0335,0.0037,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.0169,0.9957,0.0002</t>
-  </si>
-  <si>
-    <t>0.0206,0.0618,0.9455,0.0064</t>
-  </si>
-  <si>
-    <t>0.0413,0.3304,0.5932,0.0348</t>
-  </si>
-  <si>
-    <t>0.0015,0.0322,0.9880,0.0012</t>
-  </si>
-  <si>
-    <t>0.0089,0.0386,0.9788,0.0008</t>
-  </si>
-  <si>
-    <t>0.0350,0.0089,0.9633,0.0025</t>
-  </si>
-  <si>
-    <t>0.0210,0.0136,0.9705,0.0008</t>
-  </si>
-  <si>
-    <t>0.0788,0.0598,0.8696,0.0065</t>
-  </si>
-  <si>
-    <t>0.2774,0.0410,0.8040,0.0028</t>
-  </si>
-  <si>
-    <t>0.3932,0.1346,0.4691,0.0033</t>
-  </si>
-  <si>
-    <t>0.2641,0.4760,0.2740,0.0148</t>
-  </si>
-  <si>
-    <t>0.1937,0.2121,0.5686,0.0013</t>
-  </si>
-  <si>
-    <t>0.4863,0.0362,0.5115,0.0010</t>
-  </si>
-  <si>
-    <t>0.4582,0.3132,0.3271,0.0422</t>
-  </si>
-  <si>
-    <t>0.4121,0.0596,0.5807,0.0128</t>
-  </si>
-  <si>
-    <t>0.8522,0.1088,0.0295,0.0002</t>
-  </si>
-  <si>
-    <t>0.8851,0.2311,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9363,0.1117,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.9219,0.1427,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9445,0.1204,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.7758,0.0226,0.2424,0.0103</t>
-  </si>
-  <si>
-    <t>0.8322,0.0058,0.2107,0.0084</t>
-  </si>
-  <si>
-    <t>0.7906,0.0281,0.1019,0.0696</t>
-  </si>
-  <si>
-    <t>0.8044,0.0020,0.1665,0.0202</t>
-  </si>
-  <si>
-    <t>0.9091,0.0094,0.1048,0.0051</t>
-  </si>
-  <si>
-    <t>0.0491,0.0396,0.9175,0.0198</t>
-  </si>
-  <si>
-    <t>0.0645,0.0836,0.8786,0.0023</t>
-  </si>
-  <si>
-    <t>0.0119,0.4919,0.9305,0.0031</t>
-  </si>
-  <si>
-    <t>0.1661,0.0610,0.8201,0.0089</t>
-  </si>
-  <si>
-    <t>0.0394,0.5764,0.7579,0.0018</t>
-  </si>
-  <si>
-    <t>0.9908,0.0076,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9959,0.0028,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9918,0.0042,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9877,0.0107,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9904,0.0084,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9844,0.0188,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9892,0.0043,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9931,0.0025,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.0370,0.0415,0.9558,0.0014</t>
-  </si>
-  <si>
-    <t>0.3045,0.2879,0.5705,0.0049</t>
-  </si>
-  <si>
-    <t>0.9411,0.0078,0.0083,0.0277</t>
-  </si>
-  <si>
-    <t>0.0195,0.0189,0.9739,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0114,0.9911,0.0026</t>
-  </si>
-  <si>
-    <t>0.0377,0.0568,0.9299,0.0011</t>
-  </si>
-  <si>
-    <t>0.0013,0.0162,0.9943,0.0007</t>
-  </si>
-  <si>
-    <t>0.0371,0.0652,0.8872,0.0018</t>
-  </si>
-  <si>
-    <t>0.0328,0.0156,0.9778,0.0005</t>
-  </si>
-  <si>
-    <t>0.0111,0.0270,0.9712,0.0008</t>
-  </si>
-  <si>
-    <t>0.0584,0.1662,0.7764,0.0886</t>
-  </si>
-  <si>
-    <t>0.6363,0.0049,0.3089,0.0347</t>
-  </si>
-  <si>
-    <t>0.8039,0.0049,0.3503,0.0047</t>
-  </si>
-  <si>
-    <t>0.8290,0.0248,0.1313,0.0113</t>
-  </si>
-  <si>
-    <t>0.9925,0.0039,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9932,0.0073,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9930,0.0071,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9845,0.0286,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9943,0.0045,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9917,0.0056,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0019,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9829,0.0106,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.0074,0.5881,0.6464,0.0025</t>
-  </si>
-  <si>
-    <t>0.0019,0.1015,0.9757,0.0006</t>
-  </si>
-  <si>
-    <t>0.0737,0.1072,0.8159,0.0011</t>
-  </si>
-  <si>
-    <t>0.0418,0.1113,0.8494,0.0044</t>
-  </si>
-  <si>
-    <t>0.0040,0.0011,0.9915,0.0034</t>
-  </si>
-  <si>
-    <t>0.1789,0.0210,0.8015,0.0473</t>
-  </si>
-  <si>
-    <t>0.1000,0.0405,0.8802,0.0086</t>
-  </si>
-  <si>
-    <t>0.0288,0.0198,0.9457,0.0348</t>
-  </si>
-  <si>
-    <t>0.7197,0.0056,0.0908,0.1240</t>
-  </si>
-  <si>
-    <t>0.0562,0.0728,0.0042,0.9637</t>
-  </si>
-  <si>
-    <t>0.1738,0.0008,0.0005,0.9498</t>
-  </si>
-  <si>
-    <t>0.0084,0.0001,0.0008,0.9958</t>
-  </si>
-  <si>
-    <t>0.0070,0.0006,0.0001,0.9971</t>
-  </si>
-  <si>
-    <t>0.7485,0.0617,0.0087,0.1932</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.6127,0.1789,0.0014,0.0850</t>
+  </si>
+  <si>
+    <t>0.0534,0.0099,0.0011,0.9701</t>
+  </si>
+  <si>
+    <t>0.3985,0.0273,0.0050,0.6994</t>
+  </si>
+  <si>
+    <t>0.4212,0.0045,0.0032,0.8018</t>
+  </si>
+  <si>
+    <t>0.9964,0.0014,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0005,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9953,0.0016,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9973,0.0019,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0048,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9937,0.0020,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.7345,0.0482,0.2363,0.0089</t>
+  </si>
+  <si>
+    <t>0.1581,0.0388,0.8446,0.0073</t>
+  </si>
+  <si>
+    <t>0.1708,0.1919,0.6184,0.0032</t>
+  </si>
+  <si>
+    <t>0.1371,0.0234,0.8773,0.0013</t>
+  </si>
+  <si>
+    <t>0.8768,0.0343,0.0815,0.0028</t>
+  </si>
+  <si>
+    <t>0.0113,0.9884,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.1589,0.9026,0.0088,0.0004</t>
+  </si>
+  <si>
+    <t>0.3094,0.7392,0.0341,0.0035</t>
+  </si>
+  <si>
+    <t>0.0204,0.9817,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0178,0.9814,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.3250,0.0061,0.7898,0.0072</t>
+  </si>
+  <si>
+    <t>0.4834,0.0367,0.5527,0.0089</t>
+  </si>
+  <si>
+    <t>0.0937,0.0032,0.9620,0.0009</t>
+  </si>
+  <si>
+    <t>0.0934,0.0250,0.8651,0.0139</t>
+  </si>
+  <si>
+    <t>0.3396,0.0077,0.8327,0.0009</t>
+  </si>
+  <si>
+    <t>0.0626,0.0149,0.9412,0.0018</t>
+  </si>
+  <si>
+    <t>0.0083,0.0026,0.9817,0.0253</t>
+  </si>
+  <si>
+    <t>0.6355,0.4302,0.0194,0.0065</t>
+  </si>
+  <si>
+    <t>0.7441,0.1822,0.0954,0.0045</t>
+  </si>
+  <si>
+    <t>0.0145,0.0294,0.9729,0.0164</t>
+  </si>
+  <si>
+    <t>0.0242,0.8673,0.2317,0.0011</t>
+  </si>
+  <si>
+    <t>0.8240,0.1910,0.0157,0.0043</t>
+  </si>
+  <si>
+    <t>0.4572,0.1454,0.5441,0.0024</t>
+  </si>
+  <si>
+    <t>0.6118,0.5228,0.0131,0.0011</t>
+  </si>
+  <si>
+    <t>0.0356,0.9386,0.1055,0.0026</t>
+  </si>
+  <si>
+    <t>0.0245,0.7955,0.3012,0.0122</t>
+  </si>
+  <si>
+    <t>0.0400,0.2045,0.9412,0.0049</t>
+  </si>
+  <si>
+    <t>0.0771,0.4255,0.8229,0.0331</t>
+  </si>
+  <si>
+    <t>0.1241,0.0088,0.8777,0.0183</t>
+  </si>
+  <si>
+    <t>0.0421,0.0423,0.9170,0.0036</t>
+  </si>
+  <si>
+    <t>0.0038,0.9860,0.0131,0.0003</t>
+  </si>
+  <si>
+    <t>0.0238,0.1039,0.9380,0.0015</t>
+  </si>
+  <si>
+    <t>0.0033,0.8964,0.0128,0.7560</t>
+  </si>
+  <si>
+    <t>0.0024,0.9911,0.0023,0.0034</t>
+  </si>
+  <si>
+    <t>0.0042,0.9755,0.0238,0.0054</t>
+  </si>
+  <si>
+    <t>0.0006,0.9949,0.0178,0.0060</t>
+  </si>
+  <si>
+    <t>0.0111,0.2180,0.9032,0.0019</t>
+  </si>
+  <si>
+    <t>0.0009,0.0424,0.9953,0.0002</t>
+  </si>
+  <si>
+    <t>0.2060,0.0243,0.8388,0.0055</t>
+  </si>
+  <si>
+    <t>0.0477,0.0050,0.9598,0.0019</t>
+  </si>
+  <si>
+    <t>0.0012,0.0016,0.9966,0.0014</t>
+  </si>
+  <si>
+    <t>0.0055,0.0208,0.9784,0.0013</t>
+  </si>
+  <si>
+    <t>0.9312,0.1640,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9812,0.0184,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.9826,0.0115,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.0244,0.0255,0.9755,0.0009</t>
+  </si>
+  <si>
+    <t>0.9772,0.0189,0.0020,0.0012</t>
+  </si>
+  <si>
+    <t>0.9782,0.0312,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9716,0.0467,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.9223,0.8689,0.0001</t>
+  </si>
+  <si>
+    <t>0.0716,0.0752,0.8648,0.0027</t>
+  </si>
+  <si>
+    <t>0.0070,0.0619,0.9797,0.0017</t>
+  </si>
+  <si>
+    <t>0.0005,0.9711,0.9209,0.0001</t>
+  </si>
+  <si>
+    <t>0.0093,0.0065,0.9903,0.0003</t>
+  </si>
+  <si>
+    <t>0.0749,0.8506,0.0364,0.0004</t>
+  </si>
+  <si>
+    <t>0.0260,0.9699,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.7799,0.0306,0.3262,0.0066</t>
+  </si>
+  <si>
+    <t>0.8136,0.1182,0.0937,0.0031</t>
+  </si>
+  <si>
+    <t>0.0476,0.7889,0.0443,0.0007</t>
+  </si>
+  <si>
+    <t>0.0078,0.8760,0.7192,0.0015</t>
+  </si>
+  <si>
+    <t>0.0016,0.9389,0.8825,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.9928,0.0951,0.0030</t>
+  </si>
+  <si>
+    <t>0.0024,0.9816,0.2866,0.0009</t>
+  </si>
+  <si>
+    <t>0.0542,0.0005,0.0006,0.9824</t>
+  </si>
+  <si>
+    <t>0.0075,0.0227,0.0003,0.9945</t>
+  </si>
+  <si>
+    <t>0.0043,0.0010,0.0004,0.9971</t>
+  </si>
+  <si>
+    <t>0.0643,0.0057,0.0182,0.9366</t>
+  </si>
+  <si>
+    <t>0.0165,0.0034,0.0066,0.9814</t>
+  </si>
+  <si>
+    <t>0.0047,0.0110,0.0011,0.9958</t>
+  </si>
+  <si>
+    <t>0.0018,0.9387,0.7854,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.8812,0.9541,0.0002</t>
+  </si>
+  <si>
+    <t>0.0208,0.8589,0.4201,0.0210</t>
+  </si>
+  <si>
+    <t>0.0104,0.5594,0.9226,0.0008</t>
+  </si>
+  <si>
+    <t>0.0036,0.9470,0.6920,0.0004</t>
+  </si>
+  <si>
+    <t>0.0116,0.7582,0.6240,0.0011</t>
+  </si>
+  <si>
+    <t>0.9894,0.0129,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9865,0.0092,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9797,0.0196,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9960,0.0020,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9941,0.0034,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0032,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9883,0.0153,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9796,0.0332,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9954,0.0008,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0016,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0033,0.9964,0.0034</t>
+  </si>
+  <si>
+    <t>0.0072,0.3660,0.9347,0.0035</t>
+  </si>
+  <si>
+    <t>0.9087,0.0022,0.0603,0.0104</t>
+  </si>
+  <si>
+    <t>0.1840,0.0686,0.7340,0.0172</t>
+  </si>
+  <si>
+    <t>0.0226,0.9785,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.1005,0.9257,0.0057,0.0019</t>
+  </si>
+  <si>
+    <t>0.1354,0.9099,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.2491,0.8101,0.0107,0.0010</t>
+  </si>
+  <si>
+    <t>0.0556,0.9575,0.0043,0.0010</t>
+  </si>
+  <si>
+    <t>0.0171,0.9778,0.0061,0.0003</t>
+  </si>
+  <si>
+    <t>0.5386,0.6112,0.0116,0.0021</t>
+  </si>
+  <si>
+    <t>0.5386,0.0802,0.4295,0.0091</t>
+  </si>
+  <si>
+    <t>0.1319,0.0197,0.8829,0.0023</t>
+  </si>
+  <si>
+    <t>0.5483,0.3418,0.1099,0.0047</t>
+  </si>
+  <si>
+    <t>0.4473,0.0616,0.5770,0.0110</t>
+  </si>
+  <si>
+    <t>0.0233,0.0632,0.0071,0.9760</t>
+  </si>
+  <si>
+    <t>0.0012,0.9958,0.0056,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.9920,0.0302,0.0094</t>
+  </si>
+  <si>
+    <t>0.0139,0.9710,0.0052,0.0290</t>
+  </si>
+  <si>
+    <t>0.0010,0.9922,0.2296,0.0004</t>
+  </si>
+  <si>
+    <t>0.0296,0.9716,0.0123,0.0008</t>
+  </si>
+  <si>
+    <t>0.7708,0.3383,0.0094,0.0020</t>
+  </si>
+  <si>
+    <t>0.4314,0.7058,0.0092,0.0007</t>
+  </si>
+  <si>
+    <t>0.9782,0.0205,0.0013,0.0020</t>
+  </si>
+  <si>
+    <t>0.9823,0.0192,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9801,0.0074,0.0002,0.0042</t>
+  </si>
+  <si>
+    <t>0.9751,0.0165,0.0077,0.0015</t>
+  </si>
+  <si>
+    <t>0.9913,0.0016,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9877,0.0066,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9835,0.0090,0.0026,0.0015</t>
+  </si>
+  <si>
+    <t>0.9873,0.0035,0.0080,0.0006</t>
+  </si>
+  <si>
+    <t>0.0088,0.4670,0.9340,0.0005</t>
+  </si>
+  <si>
+    <t>0.0036,0.6935,0.8662,0.0003</t>
+  </si>
+  <si>
+    <t>0.0030,0.3747,0.9539,0.0015</t>
+  </si>
+  <si>
+    <t>0.0439,0.0203,0.9520,0.0006</t>
+  </si>
+  <si>
+    <t>0.7240,0.1115,0.1376,0.0225</t>
+  </si>
+  <si>
+    <t>0.7829,0.0113,0.3284,0.0056</t>
+  </si>
+  <si>
+    <t>0.2052,0.0034,0.8087,0.0364</t>
+  </si>
+  <si>
+    <t>0.5692,0.1465,0.2765,0.0083</t>
+  </si>
+  <si>
+    <t>0.0304,0.0035,0.0006,0.9874</t>
+  </si>
+  <si>
+    <t>0.0007,0.0083,0.0009,0.9979</t>
+  </si>
+  <si>
+    <t>0.0168,0.0286,0.0120,0.9737</t>
+  </si>
+  <si>
+    <t>0.0629,0.0011,0.0008,0.9801</t>
+  </si>
+  <si>
+    <t>0.0011,0.7940,0.9026,0.0020</t>
+  </si>
+  <si>
+    <t>0.9520,0.0828,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0625,0.9455,0.0013,0.0037</t>
+  </si>
+  <si>
+    <t>0.9842,0.0022,0.0004,0.0058</t>
+  </si>
+  <si>
+    <t>0.5466,0.5126,0.0374,0.0019</t>
+  </si>
+  <si>
+    <t>0.9828,0.0039,0.0079,0.0012</t>
+  </si>
+  <si>
+    <t>0.9142,0.0021,0.0073,0.0811</t>
+  </si>
+  <si>
+    <t>0.9719,0.0182,0.0082,0.0011</t>
+  </si>
+  <si>
+    <t>0.0229,0.3875,0.8569,0.0219</t>
+  </si>
+  <si>
+    <t>0.7880,0.0028,0.0098,0.2323</t>
+  </si>
+  <si>
+    <t>0.9536,0.0075,0.0047,0.0258</t>
+  </si>
+  <si>
+    <t>0.7669,0.2170,0.0120,0.0115</t>
+  </si>
+  <si>
+    <t>0.8421,0.1016,0.0431,0.0035</t>
+  </si>
+  <si>
+    <t>0.6185,0.4832,0.0226,0.0102</t>
+  </si>
+  <si>
+    <t>0.2390,0.7153,0.0902,0.0108</t>
+  </si>
+  <si>
+    <t>0.7630,0.1843,0.0594,0.0047</t>
+  </si>
+  <si>
+    <t>0.9114,0.0544,0.0167,0.0068</t>
+  </si>
+  <si>
+    <t>0.9870,0.0120,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.9671,0.0132,0.0017,0.0111</t>
+  </si>
+  <si>
+    <t>0.9931,0.0010,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9933,0.0013,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.9878,0.0078,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.9945,0.0024,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9937,0.0014,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9948,0.0011,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.8006,0.3263,0.0015,0.0020</t>
+  </si>
+  <si>
+    <t>0.1838,0.8468,0.0108,0.0003</t>
+  </si>
+  <si>
+    <t>0.5555,0.5546,0.0146,0.0008</t>
+  </si>
+  <si>
+    <t>0.1102,0.1616,0.9263,0.0004</t>
+  </si>
+  <si>
+    <t>0.8994,0.1795,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9569,0.0429,0.0055,0.0036</t>
+  </si>
+  <si>
+    <t>0.9882,0.0047,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.5757,0.5150,0.0118,0.0025</t>
+  </si>
+  <si>
+    <t>0.0053,0.0788,0.9890,0.0002</t>
+  </si>
+  <si>
+    <t>0.9697,0.0387,0.0040,0.0006</t>
+  </si>
+  <si>
+    <t>0.0030,0.0023,0.9940,0.0016</t>
+  </si>
+  <si>
+    <t>0.0054,0.3267,0.9543,0.0021</t>
+  </si>
+  <si>
+    <t>0.0408,0.0237,0.9267,0.0176</t>
+  </si>
+  <si>
+    <t>0.0062,0.1336,0.9721,0.0003</t>
+  </si>
+  <si>
+    <t>0.0243,0.1424,0.9214,0.0010</t>
+  </si>
+  <si>
+    <t>0.0135,0.0014,0.9897,0.0008</t>
+  </si>
+  <si>
+    <t>0.0063,0.0074,0.9908,0.0003</t>
+  </si>
+  <si>
+    <t>0.2859,0.0554,0.7168,0.0039</t>
+  </si>
+  <si>
+    <t>0.0468,0.1642,0.8431,0.0044</t>
+  </si>
+  <si>
+    <t>0.0886,0.0154,0.9094,0.0050</t>
+  </si>
+  <si>
+    <t>0.3117,0.1016,0.5975,0.0019</t>
+  </si>
+  <si>
+    <t>0.2550,0.2809,0.3477,0.0007</t>
+  </si>
+  <si>
+    <t>0.2147,0.3687,0.3076,0.0031</t>
+  </si>
+  <si>
+    <t>0.4908,0.1915,0.3686,0.0355</t>
+  </si>
+  <si>
+    <t>0.2990,0.0829,0.6296,0.0150</t>
+  </si>
+  <si>
+    <t>0.5027,0.5580,0.0231,0.0011</t>
+  </si>
+  <si>
+    <t>0.8483,0.2255,0.0064,0.0003</t>
+  </si>
+  <si>
+    <t>0.8341,0.2717,0.0091,0.0005</t>
+  </si>
+  <si>
+    <t>0.9275,0.0992,0.0039,0.0038</t>
+  </si>
+  <si>
+    <t>0.9873,0.0200,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.6325,0.1268,0.2212,0.0491</t>
+  </si>
+  <si>
+    <t>0.8099,0.0174,0.2489,0.0057</t>
+  </si>
+  <si>
+    <t>0.8463,0.0090,0.0540,0.0499</t>
+  </si>
+  <si>
+    <t>0.4255,0.0882,0.5493,0.0232</t>
+  </si>
+  <si>
+    <t>0.8488,0.0216,0.1242,0.0070</t>
+  </si>
+  <si>
+    <t>0.0040,0.0098,0.9718,0.0582</t>
+  </si>
+  <si>
+    <t>0.0561,0.6946,0.5963,0.0204</t>
+  </si>
+  <si>
+    <t>0.0389,0.3092,0.8418,0.0072</t>
+  </si>
+  <si>
+    <t>0.2889,0.1669,0.6306,0.0589</t>
+  </si>
+  <si>
+    <t>0.0598,0.2622,0.7525,0.0008</t>
+  </si>
+  <si>
+    <t>0.9955,0.0023,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9931,0.0046,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0008,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9061,0.1556,0.0098,0.0011</t>
+  </si>
+  <si>
+    <t>0.9926,0.0072,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9825,0.0211,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9957,0.0005,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9935,0.0036,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0191,0.0246,0.9813,0.0005</t>
+  </si>
+  <si>
+    <t>0.1089,0.6892,0.2858,0.0027</t>
+  </si>
+  <si>
+    <t>0.7464,0.0949,0.0541,0.1152</t>
+  </si>
+  <si>
+    <t>0.0334,0.0074,0.9796,0.0006</t>
+  </si>
+  <si>
+    <t>0.0139,0.0252,0.9672,0.0043</t>
+  </si>
+  <si>
+    <t>0.0143,0.2500,0.9241,0.0005</t>
+  </si>
+  <si>
+    <t>0.0041,0.0077,0.9944,0.0003</t>
+  </si>
+  <si>
+    <t>0.0177,0.0191,0.9686,0.0020</t>
+  </si>
+  <si>
+    <t>0.0022,0.0201,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0668,0.0129,0.9342,0.0009</t>
+  </si>
+  <si>
+    <t>0.2692,0.4605,0.2789,0.0211</t>
+  </si>
+  <si>
+    <t>0.8778,0.0016,0.1725,0.0051</t>
+  </si>
+  <si>
+    <t>0.8879,0.0012,0.2175,0.0025</t>
+  </si>
+  <si>
+    <t>0.8749,0.0035,0.1135,0.0124</t>
+  </si>
+  <si>
+    <t>0.9867,0.0159,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9785,0.0435,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0034,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9797,0.0253,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9932,0.0014,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9921,0.0076,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0046,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9860,0.0073,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.0441,0.6707,0.3184,0.0004</t>
+  </si>
+  <si>
+    <t>0.0160,0.1151,0.9293,0.0033</t>
+  </si>
+  <si>
+    <t>0.0111,0.0858,0.9426,0.0020</t>
+  </si>
+  <si>
+    <t>0.0746,0.0821,0.8666,0.0020</t>
+  </si>
+  <si>
+    <t>0.0024,0.0032,0.9935,0.0024</t>
+  </si>
+  <si>
+    <t>0.2743,0.0634,0.6075,0.0898</t>
+  </si>
+  <si>
+    <t>0.0926,0.0216,0.8957,0.0094</t>
+  </si>
+  <si>
+    <t>0.0203,0.0202,0.9312,0.0498</t>
+  </si>
+  <si>
+    <t>0.2147,0.0009,0.0031,0.9068</t>
+  </si>
+  <si>
+    <t>0.0525,0.0187,0.0017,0.9741</t>
+  </si>
+  <si>
+    <t>0.0596,0.0197,0.0043,0.9652</t>
+  </si>
+  <si>
+    <t>0.0057,0.0001,0.0001,0.9980</t>
+  </si>
+  <si>
+    <t>0.0142,0.0008,0.0004,0.9928</t>
+  </si>
+  <si>
+    <t>0.9080,0.0249,0.0083,0.0419</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2144,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2942,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3603,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3894,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,10 +4454,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5168,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,10 +5336,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
